--- a/VFN/VFN_demo.xlsx
+++ b/VFN/VFN_demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paiasnodkar.1\GSpec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paiasnodkar.1\GSpec\VFN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324BA877-EA7E-41F6-8632-DC63FE91D4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA886F18-F6FC-4E33-A536-36D278C12345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="5" activeTab="7" xr2:uid="{20D83020-A72A-4097-8652-2E6CA5F9C6E2}"/>
   </bookViews>
@@ -49,6 +49,8 @@
     <author>tc={AA843CEA-79DD-44FF-9669-6A1E03DF20DB}</author>
     <author>tc={DCCACE67-3749-416B-826F-346A52B4E14B}</author>
     <author>tc={20B5632E-6582-4AFA-9C24-53AE806C8770}</author>
+    <author>tc={E17A195B-303A-4BA8-8C61-ABA6CCDDC527}</author>
+    <author>tc={9E6E7B2B-FCDB-457F-9604-6F5E698829DC}</author>
   </authors>
   <commentList>
     <comment ref="A78" authorId="0" shapeId="0" xr:uid="{56BC5293-D2D8-41A7-BE48-0EBFD4ACB558}">
@@ -84,6 +86,22 @@
       </text>
     </comment>
     <comment ref="A280" authorId="4" shapeId="0" xr:uid="{20B5632E-6582-4AFA-9C24-53AE806C8770}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Aligned extremes to have ~same power</t>
+      </text>
+    </comment>
+    <comment ref="A450" authorId="5" shapeId="0" xr:uid="{E17A195B-303A-4BA8-8C61-ABA6CCDDC527}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Aligned extremes to have ~same power</t>
+      </text>
+    </comment>
+    <comment ref="A517" authorId="6" shapeId="0" xr:uid="{9E6E7B2B-FCDB-457F-9604-6F5E698829DC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -136,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="51">
   <si>
     <t>x</t>
   </si>
@@ -283,6 +301,12 @@
   </si>
   <si>
     <t>(4/28/22) TRIAL 1:</t>
+  </si>
+  <si>
+    <t>(3/13/23) TRIAL 1:</t>
+  </si>
+  <si>
+    <t>(3/13/23) TRIAL 2:</t>
   </si>
 </sst>
 </file>
@@ -8244,6 +8268,805 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Throughput vs. separation</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>+x, trial 1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Moving input fiber, x'!$C$451:$C$483</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Moving input fiber, x'!$E$451:$E$483</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>6.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.56399999999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.92400000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2549999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.49</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.42</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1679999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.93200000000000005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69099999999999995</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.45700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.29599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.20899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.215</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-EC3D-444D-A92B-D13B62F9EDB5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>+x, trial 2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Moving input fiber, x'!$C$484:$C$516</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Moving input fiber, x'!$E$484:$E$516</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.11700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.14699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.221</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.34300000000000003</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.57299999999999995</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.84899999999999998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.101</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.3140000000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.371</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.272</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.0329999999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.78200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.66900000000000004</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.126</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-EC3D-444D-A92B-D13B62F9EDB5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1112939583"/>
+        <c:axId val="1112969119"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1112939583"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1112969119"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1112969119"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1112939583"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -8525,6 +9348,46 @@
 </file>
 
 <file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -12692,6 +13555,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -13016,6 +14395,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>930275</xdr:colOff>
+      <xdr:row>499</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>269875</xdr:colOff>
+      <xdr:row>514</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{185DAD71-2A07-2D18-39F1-7B4C1AF10192}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -13314,7 +14729,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -13335,6 +14750,12 @@
     <text>Aligned extremes to have ~same power</text>
   </threadedComment>
   <threadedComment ref="A280" dT="2022-04-18T17:21:12.28" personId="{E3D67FD2-858C-484E-8FEA-059CD9AFBC12}" id="{20B5632E-6582-4AFA-9C24-53AE806C8770}">
+    <text>Aligned extremes to have ~same power</text>
+  </threadedComment>
+  <threadedComment ref="A450" dT="2022-04-18T17:21:12.28" personId="{E3D67FD2-858C-484E-8FEA-059CD9AFBC12}" id="{E17A195B-303A-4BA8-8C61-ABA6CCDDC527}">
+    <text>Aligned extremes to have ~same power</text>
+  </threadedComment>
+  <threadedComment ref="A517" dT="2022-04-18T17:21:12.28" personId="{E3D67FD2-858C-484E-8FEA-059CD9AFBC12}" id="{9E6E7B2B-FCDB-457F-9604-6F5E698829DC}">
     <text>Aligned extremes to have ~same power</text>
   </threadedComment>
 </ThreadedComments>
@@ -24640,7 +26061,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8A51507-1FF1-447F-8675-E587ED41429C}">
-  <dimension ref="A1:K449"/>
+  <dimension ref="A1:K594"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="15.7265625" customWidth="1"/>
@@ -28959,13 +30380,13 @@
       <c r="B281">
         <v>5</v>
       </c>
-      <c r="D281">
+      <c r="E281">
         <v>0.01</v>
       </c>
-      <c r="E281">
+      <c r="F281">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="F281">
+      <c r="G281">
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
@@ -28976,13 +30397,13 @@
       <c r="B282">
         <v>5</v>
       </c>
-      <c r="D282">
+      <c r="E282">
         <v>0.151</v>
       </c>
-      <c r="E282">
+      <c r="F282">
         <v>0.14099999999999999</v>
       </c>
-      <c r="F282">
+      <c r="G282">
         <v>0.16200000000000001</v>
       </c>
     </row>
@@ -28993,13 +30414,13 @@
       <c r="B283">
         <v>5</v>
       </c>
-      <c r="D283">
+      <c r="E283">
         <v>0.317</v>
       </c>
-      <c r="E283">
+      <c r="F283">
         <v>0.31</v>
       </c>
-      <c r="F283">
+      <c r="G283">
         <v>0.32300000000000001</v>
       </c>
     </row>
@@ -29010,13 +30431,13 @@
       <c r="B284">
         <v>5</v>
       </c>
-      <c r="D284">
+      <c r="E284">
         <v>0.48599999999999999</v>
       </c>
-      <c r="E284">
+      <c r="F284">
         <v>0.47399999999999998</v>
       </c>
-      <c r="F284">
+      <c r="G284">
         <v>0.49299999999999999</v>
       </c>
     </row>
@@ -29027,13 +30448,13 @@
       <c r="B285">
         <v>5</v>
       </c>
-      <c r="D285">
+      <c r="E285">
         <v>0.64100000000000001</v>
       </c>
-      <c r="E285">
+      <c r="F285">
         <v>0.63300000000000001</v>
       </c>
-      <c r="F285">
+      <c r="G285">
         <v>0.64900000000000002</v>
       </c>
     </row>
@@ -29044,13 +30465,13 @@
       <c r="B286">
         <v>5</v>
       </c>
-      <c r="D286">
+      <c r="E286">
         <v>0.755</v>
       </c>
-      <c r="E286">
+      <c r="F286">
         <v>0.75</v>
       </c>
-      <c r="F286">
+      <c r="G286">
         <v>0.748</v>
       </c>
     </row>
@@ -29061,13 +30482,13 @@
       <c r="B287">
         <v>5</v>
       </c>
-      <c r="D287">
+      <c r="E287">
         <v>0.77</v>
       </c>
-      <c r="E287">
+      <c r="F287">
         <v>0.76300000000000001</v>
       </c>
-      <c r="F287">
+      <c r="G287">
         <v>0.77300000000000002</v>
       </c>
     </row>
@@ -29078,2508 +30499,4740 @@
       <c r="B288">
         <v>5</v>
       </c>
-      <c r="D288">
+      <c r="E288">
         <v>0.67600000000000005</v>
       </c>
-      <c r="E288">
+      <c r="F288">
         <v>0.67</v>
       </c>
-      <c r="F288">
+      <c r="G288">
         <v>0.68700000000000006</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>10</v>
       </c>
       <c r="B289">
         <v>5</v>
       </c>
-      <c r="D289">
+      <c r="E289">
         <v>0.53500000000000003</v>
       </c>
-      <c r="E289">
+      <c r="F289">
         <v>0.52700000000000002</v>
       </c>
-      <c r="F289">
+      <c r="G289">
         <v>0.54400000000000004</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>10.5</v>
       </c>
       <c r="B290">
         <v>5</v>
       </c>
-      <c r="D290">
+      <c r="E290">
         <v>0.39300000000000002</v>
       </c>
-      <c r="E290">
+      <c r="F290">
         <v>0.38600000000000001</v>
       </c>
-      <c r="F290">
+      <c r="G290">
         <v>0.40400000000000003</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>11</v>
       </c>
       <c r="B291">
         <v>5</v>
       </c>
-      <c r="D291">
+      <c r="E291">
         <v>0.22900000000000001</v>
       </c>
-      <c r="E291">
+      <c r="F291">
         <v>0.221</v>
       </c>
-      <c r="F291">
+      <c r="G291">
         <v>0.24</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>11.5</v>
       </c>
       <c r="B292">
         <v>5</v>
       </c>
-      <c r="D292">
+      <c r="E292">
         <v>0.11600000000000001</v>
       </c>
-      <c r="E292">
+      <c r="F292">
         <v>0.113</v>
       </c>
-      <c r="F292">
+      <c r="G292">
         <v>0.121</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>12</v>
       </c>
       <c r="B293">
         <v>5</v>
       </c>
-      <c r="D293">
+      <c r="E293">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="E293">
+      <c r="F293">
         <v>5.5E-2</v>
       </c>
-      <c r="F293">
+      <c r="G293">
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>12.5</v>
       </c>
       <c r="B294">
         <v>5</v>
       </c>
-      <c r="D294">
+      <c r="E294">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="E294">
+      <c r="F294">
         <v>3.1E-2</v>
       </c>
-      <c r="F294">
+      <c r="G294">
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>13</v>
       </c>
       <c r="B295">
         <v>5</v>
       </c>
-      <c r="D295">
-        <v>1.4E-2</v>
-      </c>
       <c r="E295">
         <v>1.4E-2</v>
       </c>
       <c r="F295">
+        <v>1.4E-2</v>
+      </c>
+      <c r="G295">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>13.5</v>
       </c>
       <c r="B296">
         <v>5</v>
       </c>
-      <c r="D296">
-        <v>7.0000000000000001E-3</v>
-      </c>
       <c r="E296">
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="F296">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="G296">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>14</v>
       </c>
       <c r="B297">
         <v>5</v>
       </c>
-      <c r="D297">
+      <c r="E297">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>14.5</v>
       </c>
       <c r="B298">
         <v>5</v>
       </c>
-      <c r="D298">
+      <c r="E298">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>15</v>
       </c>
       <c r="B299">
         <v>5</v>
       </c>
-      <c r="D299">
+      <c r="E299">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>15.5</v>
       </c>
       <c r="B300">
         <v>5</v>
       </c>
-      <c r="D300">
+      <c r="E300">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>16</v>
       </c>
       <c r="B301">
         <v>5</v>
       </c>
-      <c r="D301">
+      <c r="E301">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>15.5</v>
       </c>
       <c r="B302">
         <v>5</v>
       </c>
-      <c r="D302">
+      <c r="E302">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E302">
+      <c r="F302">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="F302">
+      <c r="G302">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>15</v>
       </c>
       <c r="B303">
         <v>5</v>
       </c>
-      <c r="D303">
+      <c r="E303">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>14.5</v>
       </c>
       <c r="B304">
         <v>5</v>
       </c>
-      <c r="D304">
+      <c r="E304">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>14</v>
       </c>
       <c r="B305">
         <v>5</v>
       </c>
-      <c r="D305">
+      <c r="E305">
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>13.5</v>
       </c>
       <c r="B306">
         <v>5</v>
       </c>
-      <c r="D306">
-        <v>1.9E-2</v>
-      </c>
       <c r="E306">
         <v>1.9E-2</v>
       </c>
       <c r="F306">
+        <v>1.9E-2</v>
+      </c>
+      <c r="G306">
         <v>0.02</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>13</v>
       </c>
       <c r="B307">
         <v>5</v>
       </c>
-      <c r="D307">
+      <c r="E307">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E307">
+      <c r="F307">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="F307">
+      <c r="G307">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>12.5</v>
       </c>
       <c r="B308">
         <v>5</v>
       </c>
-      <c r="D308">
-        <v>6.2E-2</v>
-      </c>
       <c r="E308">
         <v>6.2E-2</v>
       </c>
       <c r="F308">
+        <v>6.2E-2</v>
+      </c>
+      <c r="G308">
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>12</v>
       </c>
       <c r="B309">
         <v>5</v>
       </c>
-      <c r="D309">
+      <c r="E309">
         <v>0.154</v>
       </c>
-      <c r="E309">
+      <c r="F309">
         <v>0.15</v>
       </c>
-      <c r="F309">
+      <c r="G309">
         <v>0.159</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>11.5</v>
       </c>
       <c r="B310">
         <v>5</v>
       </c>
-      <c r="D310">
+      <c r="E310">
         <v>0.27800000000000002</v>
       </c>
-      <c r="E310">
+      <c r="F310">
         <v>0.26400000000000001</v>
       </c>
-      <c r="F310">
+      <c r="G310">
         <v>0.28299999999999997</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>11</v>
       </c>
       <c r="B311">
         <v>5</v>
       </c>
-      <c r="D311">
+      <c r="E311">
         <v>0.38800000000000001</v>
       </c>
-      <c r="E311">
+      <c r="F311">
         <v>0.377</v>
       </c>
-      <c r="F311">
+      <c r="G311">
         <v>0.40500000000000003</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>10.5</v>
       </c>
       <c r="B312">
         <v>5</v>
       </c>
-      <c r="D312">
+      <c r="E312">
         <v>0.42299999999999999</v>
       </c>
-      <c r="E312">
+      <c r="F312">
         <v>0.40899999999999997</v>
       </c>
-      <c r="F312">
+      <c r="G312">
         <v>0.43099999999999999</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>10</v>
       </c>
       <c r="B313">
         <v>5</v>
       </c>
-      <c r="D313">
+      <c r="E313">
         <v>0.67600000000000005</v>
       </c>
-      <c r="E313">
+      <c r="F313">
         <v>0.66900000000000004</v>
       </c>
-      <c r="F313">
+      <c r="G313">
         <v>0.68100000000000005</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>9.5</v>
       </c>
       <c r="B314">
         <v>5</v>
       </c>
-      <c r="D314">
+      <c r="E314">
         <v>0.752</v>
       </c>
-      <c r="E314">
+      <c r="F314">
         <v>0.74399999999999999</v>
       </c>
-      <c r="F314">
+      <c r="G314">
         <v>0.76100000000000001</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>9</v>
       </c>
       <c r="B315">
         <v>5</v>
       </c>
-      <c r="D315">
+      <c r="E315">
         <v>0.77900000000000003</v>
       </c>
-      <c r="E315">
+      <c r="F315">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F315">
+      <c r="G315">
         <v>0.79</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>8.5</v>
       </c>
       <c r="B316">
         <v>5</v>
       </c>
-      <c r="D316">
+      <c r="E316">
         <v>0.68300000000000005</v>
       </c>
-      <c r="E316">
+      <c r="F316">
         <v>0.67500000000000004</v>
       </c>
-      <c r="F316">
+      <c r="G316">
         <v>0.68799999999999994</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>8</v>
       </c>
       <c r="B317">
         <v>5</v>
       </c>
-      <c r="D317">
+      <c r="E317">
         <v>0.56699999999999995</v>
       </c>
-      <c r="E317">
+      <c r="F317">
         <v>0.55500000000000005</v>
       </c>
-      <c r="F317">
+      <c r="G317">
         <v>0.57299999999999995</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>7.5</v>
       </c>
       <c r="B318">
         <v>5</v>
       </c>
-      <c r="D318">
+      <c r="E318">
         <v>0.41199999999999998</v>
       </c>
-      <c r="E318">
+      <c r="F318">
         <v>0.4</v>
       </c>
-      <c r="F318">
+      <c r="G318">
         <v>0.42299999999999999</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>7</v>
       </c>
       <c r="B319">
         <v>5</v>
       </c>
-      <c r="D319">
+      <c r="E319">
         <v>0.25600000000000001</v>
       </c>
-      <c r="E319">
+      <c r="F319">
         <v>0.24099999999999999</v>
       </c>
-      <c r="F319">
+      <c r="G319">
         <v>0.26</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>6.5</v>
       </c>
       <c r="B320">
         <v>5</v>
       </c>
-      <c r="D320">
+      <c r="E320">
         <v>0.08</v>
       </c>
-      <c r="E320">
+      <c r="F320">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="F320">
+      <c r="G320">
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>6</v>
       </c>
       <c r="B321">
         <v>5</v>
       </c>
-      <c r="D321">
+      <c r="E321">
         <v>1.6E-2</v>
       </c>
-      <c r="E321">
+      <c r="F321">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="F321">
+      <c r="G321">
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>5.5</v>
       </c>
       <c r="B322">
         <v>5</v>
       </c>
-      <c r="D322">
+      <c r="E322">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E322">
+      <c r="F322">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="F322">
+      <c r="G322">
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>5</v>
       </c>
       <c r="B323">
         <v>5</v>
       </c>
-      <c r="D323">
+      <c r="E323">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="E323">
+      <c r="F323">
         <v>9.4E-2</v>
       </c>
-      <c r="F323">
+      <c r="G323">
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>4.5</v>
       </c>
       <c r="B324">
         <v>5</v>
       </c>
-      <c r="D324">
+      <c r="E324">
         <v>0.158</v>
       </c>
-      <c r="E324">
+      <c r="F324">
         <v>0.155</v>
       </c>
-      <c r="F324">
+      <c r="G324">
         <v>0.16</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>4</v>
       </c>
       <c r="B325">
         <v>5</v>
       </c>
-      <c r="D325">
+      <c r="E325">
         <v>0.255</v>
       </c>
-      <c r="E325">
+      <c r="F325">
         <v>0.25</v>
       </c>
-      <c r="F325">
+      <c r="G325">
         <v>0.25700000000000001</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>3.5</v>
       </c>
       <c r="B326">
         <v>5</v>
       </c>
-      <c r="D326">
+      <c r="E326">
         <v>0.312</v>
       </c>
-      <c r="E326">
+      <c r="F326">
         <v>0.307</v>
       </c>
-      <c r="F326">
+      <c r="G326">
         <v>0.316</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>3</v>
       </c>
       <c r="B327">
         <v>5</v>
       </c>
-      <c r="D327">
+      <c r="E327">
         <v>0.36399999999999999</v>
       </c>
-      <c r="E327">
+      <c r="F327">
         <v>0.36099999999999999</v>
       </c>
-      <c r="F327">
+      <c r="G327">
         <v>0.36799999999999999</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>2.5</v>
       </c>
       <c r="B328">
         <v>5</v>
       </c>
-      <c r="D328">
+      <c r="E328">
         <v>0.40500000000000003</v>
       </c>
-      <c r="E328">
+      <c r="F328">
         <v>0.40400000000000003</v>
       </c>
-      <c r="F328">
+      <c r="G328">
         <v>0.40899999999999997</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>2</v>
       </c>
       <c r="B329">
         <v>5</v>
       </c>
-      <c r="D329">
+      <c r="E329">
         <v>0.373</v>
       </c>
-      <c r="E329">
+      <c r="F329">
         <v>0.371</v>
       </c>
-      <c r="F329">
+      <c r="G329">
         <v>0.374</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>1.5</v>
       </c>
       <c r="B330">
         <v>5</v>
       </c>
-      <c r="D330">
+      <c r="E330">
         <v>0.34300000000000003</v>
       </c>
-      <c r="E330">
+      <c r="F330">
         <v>0.34200000000000003</v>
       </c>
-      <c r="F330">
+      <c r="G330">
         <v>0.34300000000000003</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>1</v>
       </c>
       <c r="B331">
         <v>5</v>
       </c>
-      <c r="D331">
+      <c r="E331">
         <v>0.28799999999999998</v>
       </c>
-      <c r="E331">
+      <c r="F331">
         <v>0.28599999999999998</v>
       </c>
-      <c r="F331">
+      <c r="G331">
         <v>0.28899999999999998</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>0.5</v>
       </c>
       <c r="B332">
         <v>5</v>
       </c>
-      <c r="D332">
-        <v>0.24299999999999999</v>
-      </c>
       <c r="E332">
         <v>0.24299999999999999</v>
       </c>
       <c r="F332">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="G332">
         <v>0.245</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>0</v>
       </c>
       <c r="B333">
         <v>5</v>
       </c>
-      <c r="D333">
+      <c r="E333">
         <v>0.2</v>
       </c>
-      <c r="E333">
+      <c r="F333">
         <v>0.19800000000000001</v>
       </c>
-      <c r="F333">
+      <c r="G333">
         <v>0.20100000000000001</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>-0.5</v>
       </c>
       <c r="B334">
         <v>5</v>
       </c>
-      <c r="D334">
+      <c r="E334">
         <v>0.14099999999999999</v>
       </c>
-      <c r="E334">
+      <c r="F334">
         <v>0.14000000000000001</v>
       </c>
-      <c r="F334">
+      <c r="G334">
         <v>0.14299999999999999</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>-1</v>
       </c>
       <c r="B335">
         <v>5</v>
       </c>
-      <c r="D335">
+      <c r="E335">
         <v>0.114</v>
       </c>
-      <c r="E335">
+      <c r="F335">
         <v>0.113</v>
       </c>
-      <c r="F335">
+      <c r="G335">
         <v>0.115</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>-1.5</v>
       </c>
       <c r="B336">
         <v>5</v>
       </c>
-      <c r="D336">
-        <v>6.9000000000000006E-2</v>
-      </c>
       <c r="E336">
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="F336">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="G336">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>-2</v>
       </c>
       <c r="B337">
         <v>5</v>
       </c>
-      <c r="D337">
-        <v>4.2999999999999997E-2</v>
-      </c>
       <c r="E337">
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="F337">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="G337">
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>-2.5</v>
       </c>
       <c r="B338">
         <v>5</v>
       </c>
-      <c r="D338">
+      <c r="E338">
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>-3</v>
       </c>
       <c r="B339">
         <v>5</v>
       </c>
-      <c r="D339">
+      <c r="E339">
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>-3.5</v>
       </c>
       <c r="B340">
         <v>5</v>
       </c>
-      <c r="D340">
+      <c r="E340">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>-4</v>
       </c>
       <c r="B341">
         <v>5</v>
       </c>
-      <c r="D341">
+      <c r="E341">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>-4.5</v>
       </c>
       <c r="B342">
         <v>5</v>
       </c>
-      <c r="D342">
+      <c r="E342">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>-5</v>
       </c>
       <c r="B343">
         <v>5</v>
       </c>
-      <c r="D343">
+      <c r="E343">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>-4.5</v>
       </c>
       <c r="B344">
         <v>5</v>
       </c>
-      <c r="D344">
+      <c r="E344">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>-4</v>
       </c>
       <c r="B345">
         <v>5</v>
       </c>
-      <c r="D345">
+      <c r="E345">
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>-3.5</v>
       </c>
       <c r="B346">
         <v>5</v>
       </c>
-      <c r="D346">
-        <v>1.4999999999999999E-2</v>
-      </c>
       <c r="E346">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="F346">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G346">
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>-3</v>
       </c>
       <c r="B347">
         <v>5</v>
       </c>
-      <c r="D347">
+      <c r="E347">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>-2.5</v>
       </c>
       <c r="B348">
         <v>5</v>
       </c>
-      <c r="D348">
+      <c r="E348">
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>-2</v>
       </c>
       <c r="B349">
         <v>5</v>
       </c>
-      <c r="D349">
-        <v>7.0999999999999994E-2</v>
-      </c>
       <c r="E349">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="F349">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="G349">
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>-1.5</v>
       </c>
       <c r="B350">
         <v>5</v>
       </c>
-      <c r="D350">
+      <c r="E350">
         <v>0.106</v>
       </c>
-      <c r="E350">
+      <c r="F350">
         <v>0.107</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>-1</v>
       </c>
       <c r="B351">
         <v>5</v>
       </c>
-      <c r="D351">
+      <c r="E351">
         <v>0.14499999999999999</v>
       </c>
-      <c r="E351">
+      <c r="F351">
         <v>0.14399999999999999</v>
       </c>
-      <c r="F351">
+      <c r="G351">
         <v>0.14599999999999999</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>-0.5</v>
       </c>
       <c r="B352">
         <v>5</v>
       </c>
-      <c r="D352">
-        <v>0.19600000000000001</v>
-      </c>
       <c r="E352">
         <v>0.19600000000000001</v>
       </c>
       <c r="F352">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="G352">
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>0</v>
       </c>
       <c r="B353">
         <v>5</v>
       </c>
-      <c r="D353">
+      <c r="E353">
         <v>0.246</v>
       </c>
-      <c r="E353">
+      <c r="F353">
         <v>0.245</v>
       </c>
-      <c r="F353">
+      <c r="G353">
         <v>0.249</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>0.5</v>
       </c>
       <c r="B354">
         <v>5</v>
       </c>
-      <c r="D354">
+      <c r="E354">
         <v>0.29599999999999999</v>
       </c>
-      <c r="E354">
+      <c r="F354">
         <v>0.29299999999999998</v>
       </c>
-      <c r="F354">
+      <c r="G354">
         <v>0.29799999999999999</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A355">
         <v>1</v>
       </c>
       <c r="B355">
         <v>5</v>
       </c>
-      <c r="D355">
+      <c r="E355">
         <v>0.32900000000000001</v>
       </c>
-      <c r="E355">
+      <c r="F355">
         <v>0.32800000000000001</v>
       </c>
-      <c r="F355">
+      <c r="G355">
         <v>0.33100000000000002</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A356">
         <v>1.5</v>
       </c>
       <c r="B356">
         <v>5</v>
       </c>
-      <c r="D356">
+      <c r="E356">
         <v>0.36599999999999999</v>
       </c>
-      <c r="E356">
+      <c r="F356">
         <v>0.36299999999999999</v>
       </c>
-      <c r="F356">
+      <c r="G356">
         <v>0.36799999999999999</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A357">
         <v>2</v>
       </c>
       <c r="B357">
         <v>5</v>
       </c>
-      <c r="D357">
+      <c r="E357">
         <v>0.371</v>
       </c>
-      <c r="E357">
+      <c r="F357">
         <v>0.37</v>
       </c>
-      <c r="F357">
+      <c r="G357">
         <v>0.372</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A358">
         <v>2.5</v>
       </c>
       <c r="B358">
         <v>5</v>
       </c>
-      <c r="D358">
+      <c r="E358">
         <v>0.34399999999999997</v>
       </c>
-      <c r="E358">
+      <c r="F358">
         <v>0.34200000000000003</v>
       </c>
-      <c r="F358">
+      <c r="G358">
         <v>0.34799999999999998</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A359">
         <v>3</v>
       </c>
       <c r="B359">
         <v>5</v>
       </c>
-      <c r="D359">
+      <c r="E359">
         <v>0.28299999999999997</v>
       </c>
-      <c r="E359">
+      <c r="F359">
         <v>0.28100000000000003</v>
       </c>
-      <c r="F359">
+      <c r="G359">
         <v>0.28499999999999998</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A360">
         <v>3.5</v>
       </c>
       <c r="B360">
         <v>5</v>
       </c>
-      <c r="D360">
+      <c r="E360">
         <v>0.20899999999999999</v>
       </c>
-      <c r="E360">
+      <c r="F360">
         <v>0.20599999999999999</v>
       </c>
-      <c r="F360">
+      <c r="G360">
         <v>0.21099999999999999</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A361">
         <v>4</v>
       </c>
       <c r="B361">
         <v>5</v>
       </c>
-      <c r="D361">
+      <c r="E361">
         <v>0.14299999999999999</v>
       </c>
-      <c r="E361">
+      <c r="F361">
         <v>0.14099999999999999</v>
       </c>
-      <c r="F361">
+      <c r="G361">
         <v>0.14599999999999999</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A362">
         <v>4.5</v>
       </c>
       <c r="B362">
         <v>5</v>
       </c>
-      <c r="D362">
+      <c r="E362">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="E362">
+      <c r="F362">
         <v>7.8E-2</v>
       </c>
-      <c r="F362">
+      <c r="G362">
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A363">
         <v>5</v>
       </c>
       <c r="B363">
         <v>5</v>
       </c>
-      <c r="D363">
+      <c r="E363">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="E363">
+      <c r="F363">
         <v>0.05</v>
       </c>
-      <c r="F363">
+      <c r="G363">
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A364">
         <v>5.5</v>
       </c>
       <c r="B364">
         <v>5</v>
       </c>
-      <c r="D364">
+      <c r="E364">
         <v>2.3E-2</v>
       </c>
-      <c r="E364">
+      <c r="F364">
         <v>0.02</v>
       </c>
-      <c r="F364">
+      <c r="G364">
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A365">
         <v>6</v>
       </c>
       <c r="B365">
         <v>5</v>
       </c>
-      <c r="D365">
+      <c r="E365">
         <v>0.14799999999999999</v>
       </c>
-      <c r="E365">
+      <c r="F365">
         <v>0.14499999999999999</v>
       </c>
-      <c r="F365">
+      <c r="G365">
         <v>0.154</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A366">
         <v>6.5</v>
       </c>
       <c r="B366">
         <v>5</v>
       </c>
-      <c r="D366">
+      <c r="E366">
         <v>0.24</v>
       </c>
-      <c r="E366">
+      <c r="F366">
         <v>0.23200000000000001</v>
       </c>
-      <c r="F366">
+      <c r="G366">
         <v>0.24299999999999999</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A367">
         <v>7</v>
       </c>
       <c r="B367">
         <v>5</v>
       </c>
-      <c r="D367">
+      <c r="E367">
         <v>0.35899999999999999</v>
       </c>
-      <c r="E367">
+      <c r="F367">
         <v>0.35399999999999998</v>
       </c>
-      <c r="F367">
+      <c r="G367">
         <v>0.36399999999999999</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A368">
         <v>7.5</v>
       </c>
       <c r="B368">
         <v>5</v>
       </c>
-      <c r="D368">
+      <c r="E368">
         <v>0.502</v>
       </c>
-      <c r="E368">
+      <c r="F368">
         <v>0.499</v>
       </c>
-      <c r="F368">
+      <c r="G368">
         <v>0.51100000000000001</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>8</v>
       </c>
       <c r="B369">
         <v>5</v>
       </c>
-      <c r="D369">
+      <c r="E369">
         <v>0.64400000000000002</v>
       </c>
-      <c r="E369">
+      <c r="F369">
         <v>0.64100000000000001</v>
       </c>
-      <c r="F369">
+      <c r="G369">
         <v>0.64900000000000002</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A370">
         <v>8.5</v>
       </c>
       <c r="B370">
         <v>5</v>
       </c>
-      <c r="D370">
+      <c r="E370">
         <v>0.67600000000000005</v>
       </c>
-      <c r="E370">
+      <c r="F370">
         <v>0.67400000000000004</v>
       </c>
-      <c r="F370">
+      <c r="G370">
         <v>0.67900000000000005</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A371">
         <v>9</v>
       </c>
       <c r="B371">
         <v>5</v>
       </c>
-      <c r="D371">
+      <c r="E371">
         <v>0.622</v>
       </c>
-      <c r="E371">
+      <c r="F371">
         <v>0.61599999999999999</v>
       </c>
-      <c r="F371">
+      <c r="G371">
         <v>0.626</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A372">
         <v>9.5</v>
       </c>
       <c r="B372">
         <v>5</v>
       </c>
-      <c r="D372">
+      <c r="E372">
         <v>0.56299999999999994</v>
       </c>
-      <c r="E372">
+      <c r="F372">
         <v>0.55700000000000005</v>
       </c>
-      <c r="F372">
+      <c r="G372">
         <v>0.56599999999999995</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A373">
         <v>10</v>
       </c>
       <c r="B373">
         <v>5</v>
       </c>
-      <c r="D373">
+      <c r="E373">
         <v>0.4</v>
       </c>
-      <c r="E373">
+      <c r="F373">
         <v>0.39400000000000002</v>
       </c>
-      <c r="F373">
+      <c r="G373">
         <v>0.40300000000000002</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A374">
         <v>10.5</v>
       </c>
       <c r="B374">
         <v>5</v>
       </c>
-      <c r="D374">
+      <c r="E374">
         <v>0.222</v>
       </c>
-      <c r="E374">
+      <c r="F374">
         <v>0.22</v>
       </c>
-      <c r="F374">
+      <c r="G374">
         <v>0.22800000000000001</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A375">
         <v>11</v>
       </c>
       <c r="B375">
         <v>5</v>
       </c>
-      <c r="D375">
+      <c r="E375">
         <v>0.14599999999999999</v>
       </c>
-      <c r="E375">
+      <c r="F375">
         <v>0.14299999999999999</v>
       </c>
-      <c r="F375">
+      <c r="G375">
         <v>0.15</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A376">
         <v>11.5</v>
       </c>
       <c r="B376">
         <v>5</v>
       </c>
-      <c r="D376">
-        <v>7.3999999999999996E-2</v>
-      </c>
       <c r="E376">
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="F376">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="G376">
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>12</v>
       </c>
       <c r="B377">
         <v>5</v>
       </c>
-      <c r="D377">
+      <c r="E377">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="E377">
+      <c r="F377">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="F377">
+      <c r="G377">
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A378">
         <v>12.5</v>
       </c>
       <c r="B378">
         <v>5</v>
       </c>
-      <c r="D378">
+      <c r="E378">
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A379">
         <v>13</v>
       </c>
       <c r="B379">
         <v>5</v>
       </c>
-      <c r="D379">
+      <c r="E379">
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A380">
         <v>13.5</v>
       </c>
       <c r="B380">
         <v>5</v>
       </c>
-      <c r="D380">
+      <c r="E380">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A381">
         <v>14</v>
       </c>
       <c r="B381">
         <v>5</v>
       </c>
-      <c r="D381">
+      <c r="E381">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A382">
         <v>14.5</v>
       </c>
       <c r="B382">
         <v>5</v>
       </c>
-      <c r="D382">
+      <c r="E382">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>15</v>
       </c>
       <c r="B383">
         <v>5</v>
       </c>
-      <c r="D383">
+      <c r="E383">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A384">
         <v>15.5</v>
       </c>
       <c r="B384">
         <v>5</v>
       </c>
-      <c r="D384">
+      <c r="E384">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A385">
         <v>16</v>
       </c>
       <c r="B385">
         <v>5</v>
       </c>
-      <c r="D385">
+      <c r="E385">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A386">
         <v>15.5</v>
       </c>
       <c r="B386">
         <v>5</v>
       </c>
-      <c r="D386">
+      <c r="E386">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A387">
         <v>15</v>
       </c>
       <c r="B387">
         <v>5</v>
       </c>
-      <c r="D387">
+      <c r="E387">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A388">
         <v>14.5</v>
       </c>
       <c r="B388">
         <v>5</v>
       </c>
-      <c r="D388">
+      <c r="E388">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A389">
         <v>14</v>
       </c>
       <c r="B389">
         <v>5</v>
       </c>
-      <c r="D389">
+      <c r="E389">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A390">
         <v>13.5</v>
       </c>
       <c r="B390">
         <v>5</v>
       </c>
-      <c r="D390">
+      <c r="E390">
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A391">
         <v>13</v>
       </c>
       <c r="B391">
         <v>5</v>
       </c>
-      <c r="D391">
+      <c r="E391">
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A392">
         <v>12.5</v>
       </c>
       <c r="B392">
         <v>5</v>
       </c>
-      <c r="D392">
+      <c r="E392">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="E392">
+      <c r="F392">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="F392">
+      <c r="G392">
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A393">
         <v>12</v>
       </c>
       <c r="B393">
         <v>5</v>
       </c>
-      <c r="D393">
+      <c r="E393">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="E393">
+      <c r="F393">
         <v>6.2E-2</v>
       </c>
-      <c r="F393">
+      <c r="G393">
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A394">
         <v>11.5</v>
       </c>
       <c r="B394">
         <v>5</v>
       </c>
-      <c r="D394">
+      <c r="E394">
         <v>0.14299999999999999</v>
       </c>
-      <c r="E394">
+      <c r="F394">
         <v>0.14099999999999999</v>
       </c>
-      <c r="F394">
+      <c r="G394">
         <v>0.14699999999999999</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A395">
         <v>11</v>
       </c>
       <c r="B395">
         <v>5</v>
       </c>
-      <c r="D395">
+      <c r="E395">
         <v>0.22600000000000001</v>
       </c>
-      <c r="E395">
+      <c r="F395">
         <v>0.223</v>
       </c>
-      <c r="F395">
+      <c r="G395">
         <v>0.23</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A396">
         <v>10.5</v>
       </c>
       <c r="B396">
         <v>5</v>
       </c>
-      <c r="D396">
+      <c r="E396">
         <v>0.40899999999999997</v>
       </c>
-      <c r="E396">
+      <c r="F396">
         <v>0.40500000000000003</v>
       </c>
-      <c r="F396">
+      <c r="G396">
         <v>0.41899999999999998</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A397">
         <v>10</v>
       </c>
       <c r="B397">
         <v>5</v>
       </c>
-      <c r="D397">
+      <c r="E397">
         <v>0.51700000000000002</v>
       </c>
-      <c r="E397">
+      <c r="F397">
         <v>0.51400000000000001</v>
       </c>
-      <c r="F397">
+      <c r="G397">
         <v>0.53</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A398">
         <v>9.5</v>
       </c>
       <c r="B398">
         <v>5</v>
       </c>
-      <c r="D398">
+      <c r="E398">
         <v>0.58199999999999996</v>
       </c>
-      <c r="E398">
+      <c r="F398">
         <v>0.57899999999999996</v>
       </c>
-      <c r="F398">
+      <c r="G398">
         <v>0.58499999999999996</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A399">
         <v>9</v>
       </c>
       <c r="B399">
         <v>5</v>
       </c>
-      <c r="D399">
+      <c r="E399">
         <v>0.68600000000000005</v>
       </c>
-      <c r="E399">
+      <c r="F399">
         <v>0.68100000000000005</v>
       </c>
-      <c r="F399">
+      <c r="G399">
         <v>0.69</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A400">
         <v>8.5</v>
       </c>
       <c r="B400">
         <v>5</v>
       </c>
-      <c r="D400">
+      <c r="E400">
         <v>0.74099999999999999</v>
       </c>
-      <c r="E400">
+      <c r="F400">
         <v>0.73899999999999999</v>
       </c>
-      <c r="F400">
+      <c r="G400">
         <v>0.74299999999999999</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A401">
         <v>8</v>
       </c>
       <c r="B401">
         <v>5</v>
       </c>
-      <c r="D401">
+      <c r="E401">
         <v>0.71199999999999997</v>
       </c>
-      <c r="E401">
+      <c r="F401">
         <v>0.70899999999999996</v>
       </c>
-      <c r="F401">
+      <c r="G401">
         <v>0.71399999999999997</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A402">
         <v>7.5</v>
       </c>
       <c r="B402">
         <v>5</v>
       </c>
-      <c r="D402">
+      <c r="E402">
         <v>0.57499999999999996</v>
       </c>
-      <c r="E402">
+      <c r="F402">
         <v>0.57199999999999995</v>
       </c>
-      <c r="F402">
+      <c r="G402">
         <v>0.58199999999999996</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A403">
         <v>7</v>
       </c>
       <c r="B403">
         <v>5</v>
       </c>
-      <c r="D403">
+      <c r="E403">
         <v>0.44600000000000001</v>
       </c>
-      <c r="E403">
+      <c r="F403">
         <v>0.441</v>
       </c>
-      <c r="F403">
+      <c r="G403">
         <v>0.45100000000000001</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A404">
         <v>6.5</v>
       </c>
       <c r="B404">
         <v>5</v>
       </c>
-      <c r="D404">
+      <c r="E404">
         <v>0.33100000000000002</v>
       </c>
-      <c r="E404">
+      <c r="F404">
         <v>0.32400000000000001</v>
       </c>
-      <c r="F404">
+      <c r="G404">
         <v>0.33500000000000002</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A405">
         <v>6</v>
       </c>
       <c r="B405">
         <v>5</v>
       </c>
-      <c r="D405">
+      <c r="E405">
         <v>0.184</v>
       </c>
-      <c r="E405">
+      <c r="F405">
         <v>0.17599999999999999</v>
       </c>
-      <c r="F405">
+      <c r="G405">
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A406">
         <v>5.5</v>
       </c>
       <c r="B406">
         <v>5</v>
       </c>
-      <c r="D406">
+      <c r="E406">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="E406">
+      <c r="F406">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="F406">
+      <c r="G406">
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A407">
         <v>5</v>
       </c>
       <c r="B407">
         <v>5</v>
       </c>
-      <c r="D407">
+      <c r="E407">
         <v>6.2E-2</v>
       </c>
-      <c r="E407">
+      <c r="F407">
         <v>0.06</v>
       </c>
-      <c r="F407">
+      <c r="G407">
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A408">
         <v>4.5</v>
       </c>
       <c r="B408">
         <v>5</v>
       </c>
-      <c r="D408">
+      <c r="E408">
         <v>0.123</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A409">
         <v>4</v>
       </c>
       <c r="B409">
         <v>5</v>
       </c>
-      <c r="D409">
+      <c r="E409">
         <v>0.17699999999999999</v>
       </c>
-      <c r="E409">
+      <c r="F409">
         <v>0.17399999999999999</v>
       </c>
-      <c r="F409">
+      <c r="G409">
         <v>0.17799999999999999</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A410">
         <v>3.5</v>
       </c>
       <c r="B410">
         <v>5</v>
       </c>
-      <c r="D410">
+      <c r="E410">
         <v>0.23100000000000001</v>
       </c>
-      <c r="E410">
+      <c r="F410">
         <v>0.22900000000000001</v>
       </c>
-      <c r="F410">
+      <c r="G410">
         <v>0.23300000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A411">
         <v>3</v>
       </c>
       <c r="B411">
         <v>5</v>
       </c>
-      <c r="D411">
+      <c r="E411">
         <v>0.29099999999999998</v>
       </c>
-      <c r="E411">
+      <c r="F411">
         <v>0.28799999999999998</v>
       </c>
-      <c r="F411">
+      <c r="G411">
         <v>0.29199999999999998</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A412">
         <v>2.5</v>
       </c>
       <c r="B412">
         <v>5</v>
       </c>
-      <c r="D412">
+      <c r="E412">
         <v>0.32800000000000001</v>
       </c>
-      <c r="E412">
+      <c r="F412">
         <v>0.32500000000000001</v>
       </c>
-      <c r="F412">
+      <c r="G412">
         <v>0.33</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A413">
         <v>2</v>
       </c>
       <c r="B413">
         <v>5</v>
       </c>
-      <c r="D413">
+      <c r="E413">
         <v>0.35099999999999998</v>
       </c>
-      <c r="E413">
+      <c r="F413">
         <v>0.34799999999999998</v>
       </c>
-      <c r="F413">
+      <c r="G413">
         <v>0.35199999999999998</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A414">
         <v>1.5</v>
       </c>
       <c r="B414">
         <v>5</v>
       </c>
-      <c r="D414">
+      <c r="E414">
         <v>0.34200000000000003</v>
       </c>
-      <c r="E414">
+      <c r="F414">
         <v>0.34100000000000003</v>
       </c>
-      <c r="F414">
+      <c r="G414">
         <v>0.34300000000000003</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A415">
         <v>1</v>
       </c>
       <c r="B415">
         <v>5</v>
       </c>
-      <c r="D415">
+      <c r="E415">
         <v>0.316</v>
       </c>
-      <c r="E415">
+      <c r="F415">
         <v>0.313</v>
       </c>
-      <c r="F415">
+      <c r="G415">
         <v>0.318</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A416">
         <v>0.5</v>
       </c>
       <c r="B416">
         <v>5</v>
       </c>
-      <c r="D416">
+      <c r="E416">
         <v>0.27300000000000002</v>
       </c>
-      <c r="E416">
+      <c r="F416">
         <v>0.27200000000000002</v>
       </c>
-      <c r="F416">
+      <c r="G416">
         <v>0.27400000000000002</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A417">
         <v>0</v>
       </c>
       <c r="B417">
         <v>5</v>
       </c>
-      <c r="D417">
+      <c r="E417">
         <v>0.24</v>
       </c>
-      <c r="E417">
+      <c r="F417">
         <v>0.23899999999999999</v>
       </c>
-      <c r="F417">
+      <c r="G417">
         <v>0.24099999999999999</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A418">
         <v>-0.5</v>
       </c>
       <c r="B418">
         <v>5</v>
       </c>
-      <c r="D418">
+      <c r="E418">
         <v>0.17599999999999999</v>
       </c>
-      <c r="E418">
+      <c r="F418">
         <v>0.17299999999999999</v>
       </c>
-      <c r="F418">
+      <c r="G418">
         <v>0.17899999999999999</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A419">
         <v>-1</v>
       </c>
       <c r="B419">
         <v>5</v>
       </c>
-      <c r="D419">
+      <c r="E419">
         <v>0.13700000000000001</v>
       </c>
-      <c r="E419">
+      <c r="F419">
         <v>0.13500000000000001</v>
       </c>
-      <c r="F419">
+      <c r="G419">
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A420">
         <v>-1.5</v>
       </c>
       <c r="B420">
         <v>5</v>
       </c>
-      <c r="D420">
+      <c r="E420">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="E420">
+      <c r="F420">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="F420">
+      <c r="G420">
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A421">
         <v>-2</v>
       </c>
       <c r="B421">
         <v>5</v>
       </c>
-      <c r="D421">
-        <v>0.06</v>
-      </c>
       <c r="E421">
         <v>0.06</v>
       </c>
       <c r="F421">
+        <v>0.06</v>
+      </c>
+      <c r="G421">
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A422">
         <v>-2.5</v>
       </c>
       <c r="B422">
         <v>5</v>
       </c>
-      <c r="D422">
+      <c r="E422">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="E422">
+      <c r="F422">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="F422">
+      <c r="G422">
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A423">
         <v>-3</v>
       </c>
       <c r="B423">
         <v>5</v>
       </c>
-      <c r="D423">
+      <c r="E423">
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A424">
         <v>-3.5</v>
       </c>
       <c r="B424">
         <v>5</v>
       </c>
-      <c r="D424">
+      <c r="E424">
         <v>0.01</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A425">
         <v>-4</v>
       </c>
       <c r="B425">
         <v>5</v>
       </c>
-      <c r="D425">
+      <c r="E425">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A426">
         <v>-4.5</v>
       </c>
       <c r="B426">
         <v>5</v>
       </c>
-      <c r="D426">
+      <c r="E426">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A427">
         <v>-5</v>
       </c>
       <c r="B427">
         <v>5</v>
       </c>
-      <c r="D427">
+      <c r="E427">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A428">
         <v>-4.5</v>
       </c>
       <c r="B428">
         <v>5</v>
       </c>
-      <c r="D428">
-        <v>0.01</v>
-      </c>
       <c r="E428">
         <v>0.01</v>
       </c>
       <c r="F428">
+        <v>0.01</v>
+      </c>
+      <c r="G428">
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A429">
         <v>-4</v>
       </c>
       <c r="B429">
         <v>5</v>
       </c>
-      <c r="D429">
+      <c r="E429">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A430">
         <v>-3.5</v>
       </c>
       <c r="B430">
         <v>5</v>
       </c>
-      <c r="D430">
+      <c r="E430">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="E430">
+      <c r="F430">
         <v>2.4E-2</v>
       </c>
-      <c r="F430">
+      <c r="G430">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A431">
         <v>-3</v>
       </c>
       <c r="B431">
         <v>5</v>
       </c>
-      <c r="D431">
-        <v>4.3999999999999997E-2</v>
-      </c>
       <c r="E431">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="F431">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="G431">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A432">
         <v>-2.5</v>
       </c>
       <c r="B432">
         <v>5</v>
       </c>
-      <c r="D432">
-        <v>6.6000000000000003E-2</v>
-      </c>
       <c r="E432">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="F432">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="G432">
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A433">
         <v>-2</v>
       </c>
       <c r="B433">
         <v>5</v>
       </c>
-      <c r="D433">
+      <c r="E433">
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A434">
         <v>-1.5</v>
       </c>
       <c r="B434">
         <v>5</v>
       </c>
-      <c r="D434">
-        <v>0.13900000000000001</v>
-      </c>
       <c r="E434">
         <v>0.13900000000000001</v>
       </c>
       <c r="F434">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="G434">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A435">
         <v>-1</v>
       </c>
       <c r="B435">
         <v>5</v>
       </c>
-      <c r="D435">
+      <c r="E435">
         <v>0.17899999999999999</v>
       </c>
-      <c r="E435">
+      <c r="F435">
         <v>0.17799999999999999</v>
       </c>
-      <c r="F435">
+      <c r="G435">
         <v>0.18</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A436">
         <v>-0.5</v>
       </c>
       <c r="B436">
         <v>5</v>
       </c>
-      <c r="D436">
+      <c r="E436">
         <v>0.22900000000000001</v>
       </c>
-      <c r="E436">
+      <c r="F436">
         <v>0.22700000000000001</v>
       </c>
-      <c r="F436">
+      <c r="G436">
         <v>0.23200000000000001</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A437">
         <v>0</v>
       </c>
       <c r="B437">
         <v>5</v>
       </c>
-      <c r="D437">
+      <c r="E437">
         <v>0.28299999999999997</v>
       </c>
-      <c r="E437">
+      <c r="F437">
         <v>0.28199999999999997</v>
       </c>
-      <c r="F437">
+      <c r="G437">
         <v>0.28599999999999998</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A438">
         <v>0.5</v>
       </c>
       <c r="B438">
         <v>5</v>
       </c>
-      <c r="D438">
+      <c r="E438">
         <v>0.32500000000000001</v>
       </c>
-      <c r="E438">
+      <c r="F438">
         <v>0.32400000000000001</v>
       </c>
-      <c r="F438">
+      <c r="G438">
         <v>0.32600000000000001</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A439">
         <v>1</v>
       </c>
       <c r="B439">
         <v>5</v>
       </c>
-      <c r="D439">
+      <c r="E439">
         <v>0.34399999999999997</v>
       </c>
-      <c r="E439">
+      <c r="F439">
         <v>0.34300000000000003</v>
       </c>
-      <c r="F439">
+      <c r="G439">
         <v>0.34399999999999997</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A440">
         <v>1.5</v>
       </c>
       <c r="B440">
         <v>5</v>
       </c>
-      <c r="D440">
+      <c r="E440">
         <v>0.34899999999999998</v>
       </c>
-      <c r="E440">
+      <c r="F440">
         <v>0.34699999999999998</v>
       </c>
-      <c r="F440">
+      <c r="G440">
         <v>0.35</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A441">
         <v>2</v>
       </c>
       <c r="B441">
         <v>5</v>
       </c>
-      <c r="D441">
+      <c r="E441">
         <v>0.32200000000000001</v>
       </c>
-      <c r="E441">
+      <c r="F441">
         <v>0.31900000000000001</v>
       </c>
-      <c r="F441">
+      <c r="G441">
         <v>0.32300000000000001</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A442">
         <v>2.5</v>
       </c>
       <c r="B442">
         <v>5</v>
       </c>
-      <c r="D442">
+      <c r="E442">
         <v>0.25700000000000001</v>
       </c>
-      <c r="E442">
+      <c r="F442">
         <v>0.249</v>
       </c>
-      <c r="F442">
+      <c r="G442">
         <v>0.25800000000000001</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A443">
         <v>3</v>
       </c>
       <c r="B443">
         <v>5</v>
       </c>
-      <c r="D443">
+      <c r="E443">
         <v>0.20200000000000001</v>
       </c>
-      <c r="E443">
+      <c r="F443">
         <v>0.2</v>
       </c>
-      <c r="F443">
+      <c r="G443">
         <v>0.20699999999999999</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A444">
         <v>3.5</v>
       </c>
       <c r="B444">
         <v>5</v>
       </c>
-      <c r="D444">
+      <c r="E444">
         <v>0.16700000000000001</v>
       </c>
-      <c r="E444">
+      <c r="F444">
         <v>0.16500000000000001</v>
       </c>
-      <c r="F444">
+      <c r="G444">
         <v>0.17</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A445">
         <v>4</v>
       </c>
       <c r="B445">
         <v>5</v>
       </c>
-      <c r="D445">
+      <c r="E445">
         <v>0.13200000000000001</v>
       </c>
-      <c r="E445">
+      <c r="F445">
         <v>0.128</v>
       </c>
-      <c r="F445">
+      <c r="G445">
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A446">
         <v>4.5</v>
       </c>
       <c r="B446">
         <v>5</v>
       </c>
-      <c r="D446">
+      <c r="E446">
         <v>0.12</v>
       </c>
-      <c r="E446">
+      <c r="F446">
         <v>0.115</v>
       </c>
-      <c r="F446">
+      <c r="G446">
         <v>0.124</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A447">
         <v>5</v>
       </c>
       <c r="B447">
         <v>5</v>
       </c>
-      <c r="D447">
+      <c r="E447">
         <v>0.14099999999999999</v>
       </c>
-      <c r="E447">
+      <c r="F447">
         <v>0.13600000000000001</v>
       </c>
-      <c r="F447">
+      <c r="G447">
         <v>0.156</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A448">
         <v>5.5</v>
       </c>
       <c r="B448">
         <v>5</v>
       </c>
-      <c r="D448">
+      <c r="E448">
         <v>0.20599999999999999</v>
       </c>
-      <c r="E448">
+      <c r="F448">
         <v>0.19800000000000001</v>
       </c>
-      <c r="F448">
+      <c r="G448">
         <v>0.21099999999999999</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A449">
         <v>6</v>
       </c>
       <c r="B449">
         <v>5</v>
       </c>
-      <c r="D449">
+      <c r="E449">
         <v>0.308</v>
       </c>
-      <c r="E449">
+      <c r="F449">
         <v>0.28899999999999998</v>
       </c>
-      <c r="F449">
+      <c r="G449">
         <v>0.313</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A450" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B450" s="2"/>
+      <c r="C450" s="2"/>
+      <c r="D450" s="2"/>
+      <c r="E450" s="2"/>
+      <c r="F450" s="2"/>
+      <c r="G450" s="2"/>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A451">
+        <v>0.5</v>
+      </c>
+      <c r="B451">
+        <v>5.5</v>
+      </c>
+      <c r="C451" cm="1">
+        <f t="array" ref="C451:C516">SQRT((A451:A516 - A451)^2 + (B451:B516 - B451)^2)</f>
+        <v>0</v>
+      </c>
+      <c r="E451">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F451">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G451">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A452">
+        <v>1</v>
+      </c>
+      <c r="B452">
+        <v>5.5</v>
+      </c>
+      <c r="C452">
+        <v>0.5</v>
+      </c>
+      <c r="E452">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="F452">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="G452">
+        <v>0.59399999999999997</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A453">
+        <v>1.5</v>
+      </c>
+      <c r="B453">
+        <v>5.5</v>
+      </c>
+      <c r="C453">
+        <v>1</v>
+      </c>
+      <c r="E453">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="F453">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="G453">
+        <v>0.93799999999999994</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A454">
+        <v>2</v>
+      </c>
+      <c r="B454">
+        <v>5.5</v>
+      </c>
+      <c r="C454">
+        <v>1.5</v>
+      </c>
+      <c r="E454">
+        <v>1.2549999999999999</v>
+      </c>
+      <c r="F454">
+        <v>1.248</v>
+      </c>
+      <c r="G454">
+        <v>1.274</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A455">
+        <v>2.5</v>
+      </c>
+      <c r="B455">
+        <v>5.5</v>
+      </c>
+      <c r="C455">
+        <v>2</v>
+      </c>
+      <c r="E455">
+        <v>1.49</v>
+      </c>
+      <c r="F455">
+        <v>1.48</v>
+      </c>
+      <c r="G455">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A456">
+        <v>3</v>
+      </c>
+      <c r="B456">
+        <v>5.5</v>
+      </c>
+      <c r="C456">
+        <v>2.5</v>
+      </c>
+      <c r="E456">
+        <v>1.42</v>
+      </c>
+      <c r="F456">
+        <v>1.38</v>
+      </c>
+      <c r="G456">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A457">
+        <v>3.5</v>
+      </c>
+      <c r="B457">
+        <v>5.5</v>
+      </c>
+      <c r="C457">
+        <v>3</v>
+      </c>
+      <c r="E457">
+        <v>1.1679999999999999</v>
+      </c>
+      <c r="F457">
+        <v>1.149</v>
+      </c>
+      <c r="G457">
+        <v>1.1779999999999999</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A458">
+        <v>4</v>
+      </c>
+      <c r="B458">
+        <v>5.5</v>
+      </c>
+      <c r="C458">
+        <v>3.5</v>
+      </c>
+      <c r="E458">
+        <v>0.93200000000000005</v>
+      </c>
+      <c r="F458">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="G458">
+        <v>0.95299999999999996</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A459">
+        <v>4.5</v>
+      </c>
+      <c r="B459">
+        <v>5.5</v>
+      </c>
+      <c r="C459">
+        <v>4</v>
+      </c>
+      <c r="E459">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="F459">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="G459">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A460">
+        <v>5</v>
+      </c>
+      <c r="B460">
+        <v>5.5</v>
+      </c>
+      <c r="C460">
+        <v>4.5</v>
+      </c>
+      <c r="E460">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="F460">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="G460">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A461">
+        <v>5.5</v>
+      </c>
+      <c r="B461">
+        <v>5.5</v>
+      </c>
+      <c r="C461">
+        <v>5</v>
+      </c>
+      <c r="E461">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="F461">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="G461">
+        <v>0.318</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A462">
+        <v>6</v>
+      </c>
+      <c r="B462">
+        <v>5.5</v>
+      </c>
+      <c r="C462">
+        <v>5.5</v>
+      </c>
+      <c r="E462">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="F462">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="G462">
+        <v>0.218</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A463">
+        <v>6.5</v>
+      </c>
+      <c r="B463">
+        <v>5.5</v>
+      </c>
+      <c r="C463">
+        <v>6</v>
+      </c>
+      <c r="E463">
+        <v>0.215</v>
+      </c>
+      <c r="F463">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="G463">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A464">
+        <v>7</v>
+      </c>
+      <c r="B464">
+        <v>5.5</v>
+      </c>
+      <c r="C464">
+        <v>6.5</v>
+      </c>
+      <c r="E464">
+        <v>0.09</v>
+      </c>
+      <c r="F464">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="G464">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A465">
+        <v>7.5</v>
+      </c>
+      <c r="B465">
+        <v>5.5</v>
+      </c>
+      <c r="C465">
+        <v>7</v>
+      </c>
+      <c r="E465">
+        <v>6.3E-2</v>
+      </c>
+      <c r="F465">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="G465">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A466">
+        <v>8</v>
+      </c>
+      <c r="B466">
+        <v>5.5</v>
+      </c>
+      <c r="C466">
+        <v>7.5</v>
+      </c>
+      <c r="E466">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="F466">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="G466">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A467">
+        <v>8.5</v>
+      </c>
+      <c r="B467">
+        <v>5.5</v>
+      </c>
+      <c r="C467">
+        <v>8</v>
+      </c>
+      <c r="E467">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="F467">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G467">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A468">
+        <v>9</v>
+      </c>
+      <c r="B468">
+        <v>5.5</v>
+      </c>
+      <c r="C468">
+        <v>8.5</v>
+      </c>
+      <c r="E468">
+        <v>0.02</v>
+      </c>
+      <c r="F468">
+        <v>1.9E-2</v>
+      </c>
+      <c r="G468">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A469">
+        <v>9.5</v>
+      </c>
+      <c r="B469">
+        <v>5.5</v>
+      </c>
+      <c r="C469">
+        <v>9</v>
+      </c>
+      <c r="E469">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A470">
+        <v>10</v>
+      </c>
+      <c r="B470">
+        <v>5.5</v>
+      </c>
+      <c r="C470">
+        <v>9.5</v>
+      </c>
+      <c r="E470">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A471">
+        <v>10.5</v>
+      </c>
+      <c r="B471">
+        <v>5.5</v>
+      </c>
+      <c r="C471">
+        <v>10</v>
+      </c>
+      <c r="E471">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A472">
+        <v>11</v>
+      </c>
+      <c r="B472">
+        <v>5.5</v>
+      </c>
+      <c r="C472">
+        <v>10.5</v>
+      </c>
+      <c r="E472">
+        <v>1.2E-2</v>
+      </c>
+      <c r="F472">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="G472">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A473">
+        <v>11.5</v>
+      </c>
+      <c r="B473">
+        <v>5.5</v>
+      </c>
+      <c r="C473">
+        <v>11</v>
+      </c>
+      <c r="E473">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A474">
+        <v>12</v>
+      </c>
+      <c r="B474">
+        <v>5.5</v>
+      </c>
+      <c r="C474">
+        <v>11.5</v>
+      </c>
+      <c r="E474">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A475">
+        <v>12.5</v>
+      </c>
+      <c r="B475">
+        <v>5.5</v>
+      </c>
+      <c r="C475">
+        <v>12</v>
+      </c>
+      <c r="E475">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A476">
+        <v>13</v>
+      </c>
+      <c r="B476">
+        <v>5.5</v>
+      </c>
+      <c r="C476">
+        <v>12.5</v>
+      </c>
+      <c r="E476">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A477">
+        <v>13.5</v>
+      </c>
+      <c r="B477">
+        <v>5.5</v>
+      </c>
+      <c r="C477">
+        <v>13</v>
+      </c>
+      <c r="E477">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A478">
+        <v>14</v>
+      </c>
+      <c r="B478">
+        <v>5.5</v>
+      </c>
+      <c r="C478">
+        <v>13.5</v>
+      </c>
+      <c r="E478">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A479">
+        <v>14.5</v>
+      </c>
+      <c r="B479">
+        <v>5.5</v>
+      </c>
+      <c r="C479">
+        <v>14</v>
+      </c>
+      <c r="E479">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A480">
+        <v>15</v>
+      </c>
+      <c r="B480">
+        <v>5.5</v>
+      </c>
+      <c r="C480">
+        <v>14.5</v>
+      </c>
+      <c r="E480">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A481">
+        <v>15.5</v>
+      </c>
+      <c r="B481">
+        <v>5.5</v>
+      </c>
+      <c r="C481">
+        <v>15</v>
+      </c>
+      <c r="E481">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A482">
+        <v>16</v>
+      </c>
+      <c r="B482">
+        <v>5.5</v>
+      </c>
+      <c r="C482">
+        <v>15.5</v>
+      </c>
+      <c r="E482">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A483">
+        <v>16.5</v>
+      </c>
+      <c r="B483">
+        <v>5.5</v>
+      </c>
+      <c r="C483">
+        <v>16</v>
+      </c>
+      <c r="E483">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A484">
+        <v>16</v>
+      </c>
+      <c r="B484">
+        <v>5.5</v>
+      </c>
+      <c r="C484">
+        <v>15.5</v>
+      </c>
+      <c r="E484">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A485">
+        <v>15.5</v>
+      </c>
+      <c r="B485">
+        <v>5.5</v>
+      </c>
+      <c r="C485">
+        <v>15</v>
+      </c>
+      <c r="E485">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A486">
+        <v>15</v>
+      </c>
+      <c r="B486">
+        <v>5.5</v>
+      </c>
+      <c r="C486">
+        <v>14.5</v>
+      </c>
+      <c r="E486">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A487">
+        <v>14.5</v>
+      </c>
+      <c r="B487">
+        <v>5.5</v>
+      </c>
+      <c r="C487">
+        <v>14</v>
+      </c>
+      <c r="E487">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A488">
+        <v>14</v>
+      </c>
+      <c r="B488">
+        <v>5.5</v>
+      </c>
+      <c r="C488">
+        <v>13.5</v>
+      </c>
+      <c r="E488">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A489">
+        <v>13.5</v>
+      </c>
+      <c r="B489">
+        <v>5.5</v>
+      </c>
+      <c r="C489">
+        <v>13</v>
+      </c>
+      <c r="E489">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A490">
+        <v>13</v>
+      </c>
+      <c r="B490">
+        <v>5.5</v>
+      </c>
+      <c r="C490">
+        <v>12.5</v>
+      </c>
+      <c r="E490">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A491">
+        <v>12.5</v>
+      </c>
+      <c r="B491">
+        <v>5.5</v>
+      </c>
+      <c r="C491">
+        <v>12</v>
+      </c>
+      <c r="E491">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A492">
+        <v>12</v>
+      </c>
+      <c r="B492">
+        <v>5.5</v>
+      </c>
+      <c r="C492">
+        <v>11.5</v>
+      </c>
+      <c r="E492">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A493">
+        <v>11.5</v>
+      </c>
+      <c r="B493">
+        <v>5.5</v>
+      </c>
+      <c r="C493">
+        <v>11</v>
+      </c>
+      <c r="E493">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A494">
+        <v>11</v>
+      </c>
+      <c r="B494">
+        <v>5.5</v>
+      </c>
+      <c r="C494">
+        <v>10.5</v>
+      </c>
+      <c r="E494">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A495">
+        <v>10.5</v>
+      </c>
+      <c r="B495">
+        <v>5.5</v>
+      </c>
+      <c r="C495">
+        <v>10</v>
+      </c>
+      <c r="E495">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A496">
+        <v>10</v>
+      </c>
+      <c r="B496">
+        <v>5.5</v>
+      </c>
+      <c r="C496">
+        <v>9.5</v>
+      </c>
+      <c r="E496">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A497">
+        <v>9.5</v>
+      </c>
+      <c r="B497">
+        <v>5.5</v>
+      </c>
+      <c r="C497">
+        <v>9</v>
+      </c>
+      <c r="E497">
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A498">
+        <v>9</v>
+      </c>
+      <c r="B498">
+        <v>5.5</v>
+      </c>
+      <c r="C498">
+        <v>8.5</v>
+      </c>
+      <c r="E498">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A499">
+        <v>8.5</v>
+      </c>
+      <c r="B499">
+        <v>5.5</v>
+      </c>
+      <c r="C499">
+        <v>8</v>
+      </c>
+      <c r="E499">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="F499">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="G499">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="500" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A500">
+        <v>8</v>
+      </c>
+      <c r="B500">
+        <v>5.5</v>
+      </c>
+      <c r="C500">
+        <v>7.5</v>
+      </c>
+      <c r="E500">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="F500">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="G500">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A501">
+        <v>7.5</v>
+      </c>
+      <c r="B501">
+        <v>5.5</v>
+      </c>
+      <c r="C501">
+        <v>7</v>
+      </c>
+      <c r="E501">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="F501">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="G501">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A502">
+        <v>7</v>
+      </c>
+      <c r="B502">
+        <v>5.5</v>
+      </c>
+      <c r="C502">
+        <v>6.5</v>
+      </c>
+      <c r="E502">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="F502">
+        <v>0.115</v>
+      </c>
+      <c r="G502">
+        <v>0.11899999999999999</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A503">
+        <v>6.5</v>
+      </c>
+      <c r="B503">
+        <v>5.5</v>
+      </c>
+      <c r="C503">
+        <v>6</v>
+      </c>
+      <c r="E503">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="F503">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="G503">
+        <v>0.14899999999999999</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A504">
+        <v>6</v>
+      </c>
+      <c r="B504">
+        <v>5.5</v>
+      </c>
+      <c r="C504">
+        <v>5.5</v>
+      </c>
+      <c r="E504">
+        <v>0.221</v>
+      </c>
+      <c r="F504">
+        <v>0.215</v>
+      </c>
+      <c r="G504">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A505">
+        <v>5.5</v>
+      </c>
+      <c r="B505">
+        <v>5.5</v>
+      </c>
+      <c r="C505">
+        <v>5</v>
+      </c>
+      <c r="E505">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="F505">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="G505">
+        <v>0.34699999999999998</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A506">
+        <v>5</v>
+      </c>
+      <c r="B506">
+        <v>5.5</v>
+      </c>
+      <c r="C506">
+        <v>4.5</v>
+      </c>
+      <c r="E506">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="F506">
+        <v>0.56299999999999994</v>
+      </c>
+      <c r="G506">
+        <v>0.58899999999999997</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A507">
+        <v>4.5</v>
+      </c>
+      <c r="B507">
+        <v>5.5</v>
+      </c>
+      <c r="C507">
+        <v>4</v>
+      </c>
+      <c r="E507">
+        <v>0.84899999999999998</v>
+      </c>
+      <c r="F507">
+        <v>0.83</v>
+      </c>
+      <c r="G507">
+        <v>0.85699999999999998</v>
+      </c>
+    </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A508">
+        <v>4</v>
+      </c>
+      <c r="B508">
+        <v>5.5</v>
+      </c>
+      <c r="C508">
+        <v>3.5</v>
+      </c>
+      <c r="E508">
+        <v>1.101</v>
+      </c>
+      <c r="F508">
+        <v>1.048</v>
+      </c>
+      <c r="G508">
+        <v>1.109</v>
+      </c>
+    </row>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A509">
+        <v>3.5</v>
+      </c>
+      <c r="B509">
+        <v>5.5</v>
+      </c>
+      <c r="C509">
+        <v>3</v>
+      </c>
+      <c r="E509">
+        <v>1.3140000000000001</v>
+      </c>
+      <c r="F509">
+        <v>1.304</v>
+      </c>
+      <c r="G509">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A510">
+        <v>3</v>
+      </c>
+      <c r="B510">
+        <v>5.5</v>
+      </c>
+      <c r="C510">
+        <v>2.5</v>
+      </c>
+      <c r="E510">
+        <v>1.371</v>
+      </c>
+      <c r="F510">
+        <v>1.3680000000000001</v>
+      </c>
+      <c r="G510">
+        <v>1.3720000000000001</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A511">
+        <v>2.5</v>
+      </c>
+      <c r="B511">
+        <v>5.5</v>
+      </c>
+      <c r="C511">
+        <v>2</v>
+      </c>
+      <c r="E511">
+        <v>1.272</v>
+      </c>
+      <c r="F511">
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="G511">
+        <v>1.2969999999999999</v>
+      </c>
+    </row>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A512">
+        <v>2</v>
+      </c>
+      <c r="B512">
+        <v>5.5</v>
+      </c>
+      <c r="C512">
+        <v>1.5</v>
+      </c>
+      <c r="E512">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="F512">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="G512">
+        <v>1.0629999999999999</v>
+      </c>
+    </row>
+    <row r="513" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A513">
+        <v>1.5</v>
+      </c>
+      <c r="B513">
+        <v>5.5</v>
+      </c>
+      <c r="C513">
+        <v>1</v>
+      </c>
+      <c r="E513">
+        <v>0.78200000000000003</v>
+      </c>
+      <c r="F513">
+        <v>0.76400000000000001</v>
+      </c>
+      <c r="G513">
+        <v>0.80200000000000005</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A514">
+        <v>1</v>
+      </c>
+      <c r="B514">
+        <v>5.5</v>
+      </c>
+      <c r="C514">
+        <v>0.5</v>
+      </c>
+      <c r="E514">
+        <v>0.66900000000000004</v>
+      </c>
+      <c r="F514">
+        <v>0.629</v>
+      </c>
+      <c r="G514">
+        <v>0.67800000000000005</v>
+      </c>
+    </row>
+    <row r="515" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A515">
+        <v>0.5</v>
+      </c>
+      <c r="B515">
+        <v>5.5</v>
+      </c>
+      <c r="C515">
+        <v>0</v>
+      </c>
+      <c r="E515">
+        <v>0.126</v>
+      </c>
+      <c r="F515">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="G515">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A516">
+        <v>0</v>
+      </c>
+      <c r="B516">
+        <v>5.5</v>
+      </c>
+      <c r="C516">
+        <v>0.5</v>
+      </c>
+      <c r="E516">
+        <v>0</v>
+      </c>
+      <c r="F516">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="G516">
+        <v>0.63600000000000001</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A517" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B517" s="2"/>
+      <c r="C517" s="2"/>
+      <c r="D517" s="2"/>
+      <c r="E517" s="2"/>
+      <c r="F517" s="2"/>
+      <c r="G517" s="2"/>
+    </row>
+    <row r="518" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A518">
+        <v>1</v>
+      </c>
+      <c r="B518">
+        <v>8.5</v>
+      </c>
+      <c r="E518">
+        <v>0.02</v>
+      </c>
+      <c r="F518">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="G518">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A519">
+        <v>1.5</v>
+      </c>
+      <c r="B519">
+        <v>8.5</v>
+      </c>
+      <c r="E519">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="F519">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="G519">
+        <v>0.72299999999999998</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A520">
+        <v>2</v>
+      </c>
+      <c r="B520">
+        <v>8.5</v>
+      </c>
+      <c r="E520">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="F520">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="G520">
+        <v>1.1839999999999999</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A521">
+        <v>2.5</v>
+      </c>
+      <c r="B521">
+        <v>8.5</v>
+      </c>
+      <c r="E521">
+        <v>1.38</v>
+      </c>
+      <c r="F521">
+        <v>1.37</v>
+      </c>
+      <c r="G521">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="522" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A522">
+        <v>3</v>
+      </c>
+      <c r="B522">
+        <v>8.5</v>
+      </c>
+      <c r="E522">
+        <v>1.44</v>
+      </c>
+      <c r="F522">
+        <v>1.43</v>
+      </c>
+      <c r="G522">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="523" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A523">
+        <v>3.5</v>
+      </c>
+      <c r="B523">
+        <v>8.5</v>
+      </c>
+      <c r="E523">
+        <v>1.3380000000000001</v>
+      </c>
+      <c r="F523">
+        <v>1.3220000000000001</v>
+      </c>
+      <c r="G523">
+        <v>1.357</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A524">
+        <v>4</v>
+      </c>
+      <c r="B524">
+        <v>8.5</v>
+      </c>
+      <c r="E524">
+        <v>1.1339999999999999</v>
+      </c>
+      <c r="F524">
+        <v>1.109</v>
+      </c>
+      <c r="G524">
+        <v>1.1479999999999999</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A525">
+        <v>4.5</v>
+      </c>
+      <c r="B525">
+        <v>8.5</v>
+      </c>
+      <c r="E525">
+        <v>0.82</v>
+      </c>
+      <c r="F525">
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="G525">
+        <v>0.84599999999999997</v>
+      </c>
+    </row>
+    <row r="526" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A526">
+        <v>5</v>
+      </c>
+      <c r="B526">
+        <v>8.5</v>
+      </c>
+      <c r="E526">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="F526">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="G526">
+        <v>0.58499999999999996</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A527">
+        <v>5.5</v>
+      </c>
+      <c r="B527">
+        <v>8.5</v>
+      </c>
+      <c r="E527">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="F527">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="G527">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="528" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A528">
+        <v>6</v>
+      </c>
+      <c r="B528">
+        <v>8.5</v>
+      </c>
+      <c r="E528">
+        <v>0.223</v>
+      </c>
+      <c r="F528">
+        <v>0.218</v>
+      </c>
+      <c r="G528">
+        <v>0.22800000000000001</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A529">
+        <v>6.5</v>
+      </c>
+      <c r="B529">
+        <v>8.5</v>
+      </c>
+      <c r="E529">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A530">
+        <v>7</v>
+      </c>
+      <c r="B530">
+        <v>8.5</v>
+      </c>
+      <c r="E530">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A531">
+        <v>7.5</v>
+      </c>
+      <c r="B531">
+        <v>8.5</v>
+      </c>
+      <c r="E531">
+        <v>8.8999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A532">
+        <v>8</v>
+      </c>
+      <c r="B532">
+        <v>8.5</v>
+      </c>
+      <c r="E532">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A533">
+        <v>8.5</v>
+      </c>
+      <c r="B533">
+        <v>8.5</v>
+      </c>
+      <c r="E533">
+        <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A534">
+        <v>9</v>
+      </c>
+      <c r="B534">
+        <v>8.5</v>
+      </c>
+      <c r="E534">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A535">
+        <v>9.5</v>
+      </c>
+      <c r="B535">
+        <v>8.5</v>
+      </c>
+      <c r="E535">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A536">
+        <v>10</v>
+      </c>
+      <c r="B536">
+        <v>8.5</v>
+      </c>
+      <c r="E536">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A537">
+        <v>10.5</v>
+      </c>
+      <c r="B537">
+        <v>8.5</v>
+      </c>
+      <c r="E537">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A538">
+        <v>11</v>
+      </c>
+      <c r="B538">
+        <v>8.5</v>
+      </c>
+      <c r="E538">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A539">
+        <v>10.5</v>
+      </c>
+      <c r="B539">
+        <v>8.5</v>
+      </c>
+      <c r="E539">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A540">
+        <v>10</v>
+      </c>
+      <c r="B540">
+        <v>8.5</v>
+      </c>
+      <c r="E540">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A541">
+        <v>9.5</v>
+      </c>
+      <c r="B541">
+        <v>8.5</v>
+      </c>
+      <c r="E541">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A542">
+        <v>9</v>
+      </c>
+      <c r="B542">
+        <v>8.5</v>
+      </c>
+      <c r="E542">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A543">
+        <v>8.5</v>
+      </c>
+      <c r="B543">
+        <v>8.5</v>
+      </c>
+      <c r="E543">
+        <v>5.8999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A544">
+        <v>8</v>
+      </c>
+      <c r="B544">
+        <v>8.5</v>
+      </c>
+      <c r="E544">
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A545">
+        <v>7.5</v>
+      </c>
+      <c r="B545">
+        <v>8.5</v>
+      </c>
+      <c r="E545">
+        <v>0.121</v>
+      </c>
+    </row>
+    <row r="546" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A546">
+        <v>7</v>
+      </c>
+      <c r="B546">
+        <v>8.5</v>
+      </c>
+      <c r="E546">
+        <v>0.159</v>
+      </c>
+    </row>
+    <row r="547" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A547">
+        <v>6.5</v>
+      </c>
+      <c r="B547">
+        <v>8.5</v>
+      </c>
+      <c r="E547">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="548" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A548">
+        <v>6</v>
+      </c>
+      <c r="B548">
+        <v>8.5</v>
+      </c>
+      <c r="E548">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="549" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A549">
+        <v>5.5</v>
+      </c>
+      <c r="B549">
+        <v>8.5</v>
+      </c>
+      <c r="E549">
+        <v>0.503</v>
+      </c>
+    </row>
+    <row r="550" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A550">
+        <v>5</v>
+      </c>
+      <c r="B550">
+        <v>8.5</v>
+      </c>
+      <c r="E550">
+        <v>0.751</v>
+      </c>
+    </row>
+    <row r="551" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A551">
+        <v>4.5</v>
+      </c>
+      <c r="B551">
+        <v>8.5</v>
+      </c>
+      <c r="E551">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="552" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A552">
+        <v>4</v>
+      </c>
+      <c r="B552">
+        <v>8.5</v>
+      </c>
+      <c r="E552">
+        <v>1.2470000000000001</v>
+      </c>
+    </row>
+    <row r="553" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A553">
+        <v>3.5</v>
+      </c>
+      <c r="B553">
+        <v>8.5</v>
+      </c>
+      <c r="E553">
+        <v>1.333</v>
+      </c>
+    </row>
+    <row r="554" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A554">
+        <v>3</v>
+      </c>
+      <c r="B554">
+        <v>8.5</v>
+      </c>
+      <c r="E554">
+        <v>1.2430000000000001</v>
+      </c>
+    </row>
+    <row r="555" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A555">
+        <v>2.5</v>
+      </c>
+      <c r="B555">
+        <v>8.5</v>
+      </c>
+      <c r="E555">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="F555">
+        <v>0.93799999999999994</v>
+      </c>
+      <c r="G555">
+        <v>0.95499999999999996</v>
+      </c>
+    </row>
+    <row r="556" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A556">
+        <v>2</v>
+      </c>
+      <c r="B556">
+        <v>8.5</v>
+      </c>
+      <c r="E556">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="F556">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="G556">
+        <v>0.69199999999999995</v>
+      </c>
+    </row>
+    <row r="557" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A557">
+        <v>1.5</v>
+      </c>
+      <c r="B557">
+        <v>8.5</v>
+      </c>
+      <c r="E557">
+        <v>0.247</v>
+      </c>
+      <c r="F557">
+        <v>0.23</v>
+      </c>
+      <c r="G557">
+        <v>0.251</v>
+      </c>
+    </row>
+    <row r="558" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A558">
+        <v>1</v>
+      </c>
+      <c r="B558">
+        <v>8.5</v>
+      </c>
+      <c r="E558">
+        <v>0.06</v>
+      </c>
+      <c r="F558">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="G558">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="559" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A559">
+        <v>0.5</v>
+      </c>
+      <c r="B559">
+        <v>8.5</v>
+      </c>
+      <c r="E559">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="F559">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="G559">
+        <v>9.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="560" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A560">
+        <v>0</v>
+      </c>
+      <c r="B560">
+        <v>8.5</v>
+      </c>
+      <c r="E560">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="F560">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="G560">
+        <v>0.44400000000000001</v>
+      </c>
+    </row>
+    <row r="561" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A561">
+        <v>-0.5</v>
+      </c>
+      <c r="B561">
+        <v>8.5</v>
+      </c>
+      <c r="E561">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="F561">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="G561">
+        <v>1.046</v>
+      </c>
+    </row>
+    <row r="562" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A562">
+        <v>-1</v>
+      </c>
+      <c r="B562">
+        <v>8.5</v>
+      </c>
+      <c r="E562">
+        <v>1.46</v>
+      </c>
+      <c r="F562">
+        <v>1.46</v>
+      </c>
+      <c r="G562">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="563" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A563">
+        <v>-1.5</v>
+      </c>
+      <c r="B563">
+        <v>8.5</v>
+      </c>
+      <c r="E563">
+        <v>1.8</v>
+      </c>
+      <c r="F563">
+        <v>1.79</v>
+      </c>
+      <c r="G563">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="564" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A564">
+        <v>-2</v>
+      </c>
+      <c r="B564">
+        <v>8.5</v>
+      </c>
+      <c r="E564">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="565" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A565">
+        <v>-2.5</v>
+      </c>
+      <c r="B565">
+        <v>8.5</v>
+      </c>
+      <c r="E565">
+        <v>1.72</v>
+      </c>
+      <c r="F565">
+        <v>1.71</v>
+      </c>
+      <c r="G565">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="566" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A566">
+        <v>-3</v>
+      </c>
+      <c r="B566">
+        <v>8.5</v>
+      </c>
+      <c r="E566">
+        <v>1.41</v>
+      </c>
+      <c r="F566">
+        <v>1.39</v>
+      </c>
+      <c r="G566">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="567" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A567">
+        <v>-3.5</v>
+      </c>
+      <c r="B567">
+        <v>8.5</v>
+      </c>
+      <c r="E567">
+        <v>1.008</v>
+      </c>
+      <c r="F567">
+        <v>0.98699999999999999</v>
+      </c>
+      <c r="G567">
+        <v>1.022</v>
+      </c>
+    </row>
+    <row r="568" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A568">
+        <v>-4</v>
+      </c>
+      <c r="B568">
+        <v>8.5</v>
+      </c>
+      <c r="E568">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="F568">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="G568">
+        <v>0.67600000000000005</v>
+      </c>
+    </row>
+    <row r="569" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A569">
+        <v>-4.5</v>
+      </c>
+      <c r="B569">
+        <v>8.5</v>
+      </c>
+      <c r="E569">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="F569">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="G569">
+        <v>0.378</v>
+      </c>
+    </row>
+    <row r="570" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A570">
+        <v>-5</v>
+      </c>
+      <c r="B570">
+        <v>8.5</v>
+      </c>
+      <c r="E570">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="F570">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="G570">
+        <v>0.17399999999999999</v>
+      </c>
+    </row>
+    <row r="571" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A571">
+        <v>-5.5</v>
+      </c>
+      <c r="B571">
+        <v>8.5</v>
+      </c>
+      <c r="E571">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="F571">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="G571">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="572" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A572">
+        <v>-6</v>
+      </c>
+      <c r="B572">
+        <v>8.5</v>
+      </c>
+      <c r="E572">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="F572">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="G572">
+        <v>5.7000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="573" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A573">
+        <v>-6.5</v>
+      </c>
+      <c r="B573">
+        <v>8.5</v>
+      </c>
+      <c r="E573">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="574" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A574">
+        <v>-7</v>
+      </c>
+      <c r="B574">
+        <v>8.5</v>
+      </c>
+      <c r="E574">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="575" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A575">
+        <v>-7.5</v>
+      </c>
+      <c r="B575">
+        <v>8.5</v>
+      </c>
+      <c r="E575">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="576" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A576">
+        <v>-8</v>
+      </c>
+      <c r="B576">
+        <v>8.5</v>
+      </c>
+      <c r="E576">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="577" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A577">
+        <v>-7.5</v>
+      </c>
+      <c r="B577">
+        <v>8.5</v>
+      </c>
+      <c r="E577">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="578" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A578">
+        <v>-7</v>
+      </c>
+      <c r="B578">
+        <v>8.5</v>
+      </c>
+      <c r="E578">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A579">
+        <v>-6.5</v>
+      </c>
+      <c r="B579">
+        <v>8.5</v>
+      </c>
+      <c r="E579">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="580" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A580">
+        <v>-6</v>
+      </c>
+      <c r="B580">
+        <v>8.5</v>
+      </c>
+      <c r="E580">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A581">
+        <v>-5.5</v>
+      </c>
+      <c r="B581">
+        <v>8.5</v>
+      </c>
+      <c r="E581">
+        <v>0.25</v>
+      </c>
+      <c r="F581">
+        <v>0.246</v>
+      </c>
+      <c r="G581">
+        <v>0.253</v>
+      </c>
+    </row>
+    <row r="582" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A582">
+        <v>-5</v>
+      </c>
+      <c r="B582">
+        <v>8.5</v>
+      </c>
+      <c r="E582">
+        <v>0.437</v>
+      </c>
+      <c r="F582">
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="G582">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="583" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A583">
+        <v>-4.5</v>
+      </c>
+      <c r="B583">
+        <v>8.5</v>
+      </c>
+      <c r="E583">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="F583">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="G583">
+        <v>0.73499999999999999</v>
+      </c>
+    </row>
+    <row r="584" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A584">
+        <v>-4</v>
+      </c>
+      <c r="B584">
+        <v>8.5</v>
+      </c>
+      <c r="E584">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="F584">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="G584">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="585" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A585">
+        <v>-3.5</v>
+      </c>
+      <c r="B585">
+        <v>8.5</v>
+      </c>
+      <c r="E585">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="586" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A586">
+        <v>-3</v>
+      </c>
+      <c r="B586">
+        <v>8.5</v>
+      </c>
+      <c r="E586">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A587">
+        <v>-2.5</v>
+      </c>
+      <c r="B587">
+        <v>8.5</v>
+      </c>
+      <c r="E587">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A588">
+        <v>-2</v>
+      </c>
+      <c r="B588">
+        <v>8.5</v>
+      </c>
+      <c r="E588">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="589" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A589">
+        <v>-1.5</v>
+      </c>
+      <c r="B589">
+        <v>8.5</v>
+      </c>
+      <c r="E589">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="590" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A590">
+        <v>-1</v>
+      </c>
+      <c r="B590">
+        <v>8.5</v>
+      </c>
+      <c r="E590">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="F590">
+        <v>1.2230000000000001</v>
+      </c>
+      <c r="G590">
+        <v>1.2470000000000001</v>
+      </c>
+    </row>
+    <row r="591" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A591">
+        <v>-0.5</v>
+      </c>
+      <c r="B591">
+        <v>8.5</v>
+      </c>
+      <c r="E591">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="F591">
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="G591">
+        <v>6.2199999999999998E-2</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A592">
+        <v>0</v>
+      </c>
+      <c r="B592">
+        <v>8.5</v>
+      </c>
+      <c r="E592">
+        <v>0.248</v>
+      </c>
+      <c r="F592">
+        <v>0.218</v>
+      </c>
+      <c r="G592">
+        <v>0.27600000000000002</v>
+      </c>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A593">
+        <v>0.5</v>
+      </c>
+      <c r="B593">
+        <v>8.5</v>
+      </c>
+      <c r="E593">
+        <v>3.9E-2</v>
+      </c>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A594">
+        <v>1</v>
+      </c>
+      <c r="B594">
+        <v>8.5</v>
+      </c>
+      <c r="E594">
+        <v>0.186</v>
+      </c>
+      <c r="F594">
+        <v>0.18</v>
+      </c>
+      <c r="G594">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
